--- a/education_forms/028_online_teaching_application_form--education_forms.xlsx
+++ b/education_forms/028_online_teaching_application_form--education_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -589,7 +589,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>application_form</t>
+          <t>application_form_2</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -612,7 +612,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>uploaded_cv</t>
+          <t>uploaded_cv_2</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -735,12 +735,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>name</t>
+          <t>name_2</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>name</t>
+          <t>Name 2</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
@@ -758,12 +758,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>name</t>
+          <t>name_3</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>name</t>
+          <t>Name 3</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
@@ -781,12 +781,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>name</t>
+          <t>name_4</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>name</t>
+          <t>Name 4</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
@@ -804,12 +804,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>name</t>
+          <t>name_5</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>name</t>
+          <t>Name 5</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
@@ -833,7 +833,7 @@
   <dimension ref="A1:C5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="26" customWidth="1" min="1" max="1"/>
+    <col width="28" customWidth="1" min="1" max="1"/>
     <col width="6" customWidth="1" min="2" max="2"/>
     <col width="7" customWidth="1" min="3" max="3"/>
   </cols>
@@ -892,7 +892,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>application_form_choices</t>
+          <t>application_form_2_choices</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -909,7 +909,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>application_form_choices</t>
+          <t>application_form_2_choices</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
